--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N102_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N102_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.27024572694387</v>
+        <v>7.356414930628379</v>
       </c>
       <c r="D2" t="n">
-        <v>41.36633878785354</v>
+        <v>6.722030053026201</v>
       </c>
       <c r="E2" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F2" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.12862795961745</v>
+        <v>7.495902043437836</v>
       </c>
       <c r="D3" t="n">
-        <v>41.8332699997563</v>
+        <v>6.797906374960398</v>
       </c>
       <c r="E3" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F3" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.45615660368909</v>
+        <v>7.874125448099477</v>
       </c>
       <c r="D4" t="n">
-        <v>46.0587873522644</v>
+        <v>7.484552944742966</v>
       </c>
       <c r="E4" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F4" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.76945641927167</v>
+        <v>6.625036668131647</v>
       </c>
       <c r="D5" t="n">
-        <v>23.29108129297435</v>
+        <v>3.784800710108333</v>
       </c>
       <c r="E5" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F5" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.99173496111872</v>
+        <v>5.848656931181793</v>
       </c>
       <c r="D6" t="n">
-        <v>8.426669674643449</v>
+        <v>1.369333822129561</v>
       </c>
       <c r="E6" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F6" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.93236737693845</v>
+        <v>2.751509698752498</v>
       </c>
       <c r="D7" t="n">
-        <v>10.59481005020855</v>
+        <v>1.721656633158889</v>
       </c>
       <c r="E7" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F7" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.7097740260806</v>
+        <v>6.127838279238098</v>
       </c>
       <c r="D8" t="n">
-        <v>9.322371174137512</v>
+        <v>1.514885315797346</v>
       </c>
       <c r="E8" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F8" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.396836826803082</v>
+        <v>0.2269859843555008</v>
       </c>
       <c r="D9" t="n">
-        <v>1.801544690426782</v>
+        <v>0.2927510121943521</v>
       </c>
       <c r="E9" t="n">
-        <v>15.41457979382442</v>
+        <v>2.504869216496468</v>
       </c>
       <c r="F9" t="n">
-        <v>16.68201379685956</v>
+        <v>2.710827241989679</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
